--- a/新建文件夹 (2)/旗舰店周报_利润下降原因分析.xlsx
+++ b/新建文件夹 (2)/旗舰店周报_利润下降原因分析.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="01-利润下降原因" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="02-关键周对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="03-口径说明" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="02-相对上一版变化" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="03-关键周对比" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -69,10 +69,6 @@
       <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="14"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="7">
@@ -134,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -181,14 +177,10 @@
     <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -278,7 +270,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>推广后利润周趋势</a:t>
+              <a:t>推广后利润周趋势（修订后）</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -688,21 +680,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>从《天猫旗舰店周报》看利润下降原因</t>
+          <t>从《天猫旗舰店周报》（已修改）看利润下降原因</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：天猫旗舰店周报_7.27-8.2.csv｜店铺级｜拆解：推广后变化 ≈ 推广前变化 − 推广投入变化</t>
+          <t>数据来源：天猫旗舰店周报_7.27-8.2.csv（用户修订版）｜店铺级｜推广后变化 ≈ 推广前变化 − 推广投入变化</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>一、利润下降原因结论</t>
+          <t>一、利润下降原因（按修订后数据）</t>
         </is>
       </c>
     </row>
@@ -718,73 +710,73 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="48" customHeight="1">
+    <row r="6" ht="46" customHeight="1">
       <c r="A6" s="5" t="n">
         <v>1</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>总览：近3个月店铺推广后利润多数为负。7月相对较好周是 7.6-7.12（-4109），随后走弱：7.13 -5144 → 7.20 -5582；7.27 回升到 -5089，8.3 又落到 -5821。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="48" customHeight="1">
+          <t>修订说明：相对上一版变化：6.1-6.7（推广后利润:3605.0-&gt;-7458.0）；6.15-6.21（推广后利润:3605.0-&gt;-7953.0）；6.22-6.28（推广后利润:3605.0-&gt;-7765.0）；6.8-6.14（推广后利润:3605.0-&gt;-8672.0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
       <c r="A7" s="6" t="n">
         <v>2</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>第一波下降（7.6→7.13）：推广后 -4109→-5144（-1035）。推广前利润 -3160，推广投入 -2604。主因：推广前利润下降（GMV同步下滑），不是推广费上升（推广费其实在降）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="48" customHeight="1">
+          <t>总览：7月较好周 7.6-7.12（推广后 -4109）后走弱；7.13 -5144 → 7.20 -5582；7.27 回升至 -5089；8.3 再降至 -5821。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
       <c r="A8" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>第二波下降（7.13→7.20）：推广后 -5144→-5582（-438）。推广前 -156，推广投入 +607。主因：推广费上升，叠加推广前利润继续小幅走弱。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="48" customHeight="1">
+          <t>第一波（7.6→7.13）：推广后 -4109→-5144（-1035）。推广前 -3160，推广投入 -2604 → 主要是推广前利润下降。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
       <c r="A9" s="6" t="n">
         <v>4</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>7.27当周（相对7.20）：推广后改善到 -5089（+493）。推广前回升 +1491 大于推广投入增加 +1028，故利润好转。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="48" customHeight="1">
+          <t>第二波（7.13→7.20）：推广后 -5144→-5582（-438）。推广前 -156，推广投入 +607 → 主要是推广费上升。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
       <c r="A10" s="5" t="n">
         <v>5</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>第三波下降（7.27→8.3）：推广后 -5089→-5821（-732）。推广前虽升 +2413，但推广投入大增 +3049，推广费上升吃掉了增量利润。主因：推广费上升。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="48" customHeight="1">
+          <t>7.27当周（相对7.20）：推广后 -5582→-5089（+493）。推广前回升超过推广费增加，利润改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
       <c r="A11" s="6" t="n">
         <v>6</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>结论（针对这份周报）：近期利润下降不是单一原因——7月中上旬主要是“生意/推广前利润走弱”；7月下旬至8月初更多是“推广费抬升过快”。店铺级报告无法定位到具体商品ID。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="48" customHeight="1">
+          <t>第三波（7.27→8.3）：推广后 -5089→-5821（-732）。推广前 +2413，推广投入 +3049 → 主要是推广费上升。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
       <c r="A12" s="5" t="n">
         <v>7</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>数据提示：6.1-6.7 至 6.22-6.28 四周推广后利润均为 3605，疑似填报重复/口径异常，分析时不作为可靠基线。</t>
+          <t>一句话：近期利润变差 = 先是推广前利润/生意走弱，后是推广费抬升过快。店铺周报无法定位商品ID。6月推广后利润已区分：[-7458.0, -8672.0, -7953.0, -7765.0]</t>
         </is>
       </c>
     </row>
@@ -826,11 +818,6 @@
           <t>主因判断</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -857,11 +844,6 @@
           <t>主要是推广前利润下降</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>GMV下滑，推广费同步下降，但前利润掉更多</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -888,11 +870,6 @@
           <t>主要是推广费上升</t>
         </is>
       </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>前利润略降，推广费明显抬升</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
@@ -919,11 +896,6 @@
           <t>本期改善</t>
         </is>
       </c>
-      <c r="G19" s="11" t="inlineStr">
-        <is>
-          <t>前利润回升超过推广费增加</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -948,11 +920,6 @@
       <c r="F20" s="8" t="inlineStr">
         <is>
           <t>主要是推广费上升</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>前利润升，但推广投入升幅更大</t>
         </is>
       </c>
     </row>
@@ -1114,74 +1081,74 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>6.1-6.7</t>
         </is>
       </c>
-      <c r="B28" s="14" t="n">
+      <c r="B28" s="10" t="n">
         <v>123012</v>
       </c>
-      <c r="C28" s="14" t="n">
+      <c r="C28" s="10" t="n">
         <v>14905</v>
       </c>
-      <c r="D28" s="15" t="n">
+      <c r="D28" s="9" t="n">
         <v>-1629</v>
       </c>
-      <c r="E28" s="14" t="n">
+      <c r="E28" s="10" t="n">
         <v>20101</v>
       </c>
-      <c r="F28" s="15" t="n">
+      <c r="F28" s="9" t="n">
         <v>-2766</v>
       </c>
-      <c r="G28" s="14" t="n">
-        <v>3605</v>
-      </c>
-      <c r="H28" s="14" t="n">
-        <v>10447</v>
-      </c>
-      <c r="I28" s="16" t="n">
+      <c r="G28" s="9" t="n">
+        <v>-7458</v>
+      </c>
+      <c r="H28" s="9" t="n">
+        <v>-616</v>
+      </c>
+      <c r="I28" s="17" t="n">
         <v>0.1816</v>
       </c>
-      <c r="J28" s="13" t="inlineStr">
-        <is>
-          <t>改善/持平</t>
+      <c r="J28" s="8" t="inlineStr">
+        <is>
+          <t>主要是推广前利润下降</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>6.8-6.14</t>
         </is>
       </c>
-      <c r="B29" s="14" t="n">
+      <c r="B29" s="10" t="n">
         <v>113858</v>
       </c>
-      <c r="C29" s="14" t="n">
+      <c r="C29" s="10" t="n">
         <v>13782</v>
       </c>
-      <c r="D29" s="15" t="n">
+      <c r="D29" s="9" t="n">
         <v>-1123</v>
       </c>
-      <c r="E29" s="14" t="n">
+      <c r="E29" s="10" t="n">
         <v>20196</v>
       </c>
-      <c r="F29" s="14" t="n">
+      <c r="F29" s="10" t="n">
         <v>95</v>
       </c>
-      <c r="G29" s="14" t="n">
-        <v>3605</v>
-      </c>
-      <c r="H29" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="16" t="n">
+      <c r="G29" s="9" t="n">
+        <v>-8672</v>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>-1214</v>
+      </c>
+      <c r="I29" s="17" t="n">
         <v>0.197</v>
       </c>
-      <c r="J29" s="13" t="inlineStr">
-        <is>
-          <t>改善/持平</t>
+      <c r="J29" s="8" t="inlineStr">
+        <is>
+          <t>主要是推广前利润下降</t>
         </is>
       </c>
     </row>
@@ -1206,11 +1173,11 @@
       <c r="F30" s="15" t="n">
         <v>-706</v>
       </c>
-      <c r="G30" s="14" t="n">
-        <v>3605</v>
-      </c>
-      <c r="H30" s="18" t="n">
-        <v>0</v>
+      <c r="G30" s="15" t="n">
+        <v>-7953</v>
+      </c>
+      <c r="H30" s="14" t="n">
+        <v>719</v>
       </c>
       <c r="I30" s="16" t="n">
         <v>0.1905</v>
@@ -1242,11 +1209,11 @@
       <c r="F31" s="15" t="n">
         <v>-2439</v>
       </c>
-      <c r="G31" s="14" t="n">
-        <v>3605</v>
-      </c>
-      <c r="H31" s="18" t="n">
-        <v>0</v>
+      <c r="G31" s="15" t="n">
+        <v>-7765</v>
+      </c>
+      <c r="H31" s="14" t="n">
+        <v>188</v>
       </c>
       <c r="I31" s="16" t="n">
         <v>0.1956</v>
@@ -1258,38 +1225,38 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>6.29-7.5</t>
         </is>
       </c>
-      <c r="B32" s="10" t="n">
+      <c r="B32" s="14" t="n">
         <v>100176</v>
       </c>
-      <c r="C32" s="10" t="n">
+      <c r="C32" s="14" t="n">
         <v>12985</v>
       </c>
-      <c r="D32" s="10" t="n">
+      <c r="D32" s="14" t="n">
         <v>1263</v>
       </c>
-      <c r="E32" s="10" t="n">
+      <c r="E32" s="14" t="n">
         <v>17357</v>
       </c>
-      <c r="F32" s="10" t="n">
+      <c r="F32" s="14" t="n">
         <v>306</v>
       </c>
-      <c r="G32" s="9" t="n">
+      <c r="G32" s="15" t="n">
         <v>-5230</v>
       </c>
-      <c r="H32" s="9" t="n">
-        <v>-8835</v>
-      </c>
-      <c r="I32" s="17" t="n">
+      <c r="H32" s="14" t="n">
+        <v>2535</v>
+      </c>
+      <c r="I32" s="16" t="n">
         <v>0.1888</v>
       </c>
-      <c r="J32" s="8" t="inlineStr">
-        <is>
-          <t>主要是推广费上升</t>
+      <c r="J32" s="13" t="inlineStr">
+        <is>
+          <t>改善/持平</t>
         </is>
       </c>
     </row>
@@ -1489,222 +1456,125 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="19" t="inlineStr">
-        <is>
-          <t>关键周绝对数对比</t>
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>修订版 vs 上一版差异明细</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>指标</t>
+          <t>周次</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>7.6-7.12</t>
+          <t>字段</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>7.13-7.19</t>
+          <t>旧值</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>7.20-7.26</t>
+          <t>新值</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>7.27-8.2</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>8.3-8.9</t>
+          <t>差额</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>GMV</t>
-        </is>
-      </c>
-      <c r="B4" s="14" t="n">
-        <v>131865</v>
+          <t>6.1-6.7</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>推广后利润</t>
+        </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>109087</v>
-      </c>
-      <c r="D4" s="14" t="n">
-        <v>107560</v>
-      </c>
-      <c r="E4" s="14" t="n">
-        <v>118941</v>
-      </c>
-      <c r="F4" s="14" t="n">
-        <v>135684</v>
+        <v>3605</v>
+      </c>
+      <c r="D4" s="15" t="n">
+        <v>-7458</v>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>-11063</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>去退金额</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="n">
-        <v>120260</v>
+          <t>6.15-6.21</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>推广后利润</t>
+        </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>100078</v>
-      </c>
-      <c r="D5" s="14" t="n">
-        <v>98481</v>
-      </c>
-      <c r="E5" s="14" t="n">
-        <v>107318</v>
-      </c>
-      <c r="F5" s="14" t="n">
-        <v>121296</v>
+        <v>3605</v>
+      </c>
+      <c r="D5" s="15" t="n">
+        <v>-7953</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>-11558</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>推广前利润</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="n">
-        <v>16861</v>
+          <t>6.22-6.28</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>推广后利润</t>
+        </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>13701</v>
-      </c>
-      <c r="D6" s="14" t="n">
-        <v>13545</v>
-      </c>
-      <c r="E6" s="14" t="n">
-        <v>15036</v>
-      </c>
-      <c r="F6" s="14" t="n">
-        <v>17449</v>
+        <v>3605</v>
+      </c>
+      <c r="D6" s="15" t="n">
+        <v>-7765</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>-11370</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>推广投入</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="n">
-        <v>20174</v>
+          <t>6.8-6.14</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>推广后利润</t>
+        </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>17570</v>
-      </c>
-      <c r="D7" s="14" t="n">
-        <v>18177</v>
-      </c>
-      <c r="E7" s="14" t="n">
-        <v>19205</v>
-      </c>
-      <c r="F7" s="14" t="n">
-        <v>22254</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>推广产出</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="n">
-        <v>96278</v>
-      </c>
-      <c r="C8" s="14" t="n">
-        <v>80093</v>
-      </c>
-      <c r="D8" s="14" t="n">
-        <v>85856</v>
-      </c>
-      <c r="E8" s="14" t="n">
-        <v>92707</v>
-      </c>
-      <c r="F8" s="14" t="n">
-        <v>98839</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>其他费用</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="n">
-        <v>2054</v>
-      </c>
-      <c r="C9" s="14" t="n">
-        <v>2405</v>
-      </c>
-      <c r="D9" s="14" t="n">
-        <v>2097</v>
-      </c>
-      <c r="E9" s="14" t="n">
-        <v>2127</v>
-      </c>
-      <c r="F9" s="14" t="n">
-        <v>2412</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>推广后利润</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="n">
-        <v>-4109</v>
-      </c>
-      <c r="C10" s="15" t="n">
-        <v>-5144</v>
-      </c>
-      <c r="D10" s="15" t="n">
-        <v>-5582</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>-5089</v>
-      </c>
-      <c r="F10" s="15" t="n">
-        <v>-5821</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>推广费率</t>
-        </is>
-      </c>
-      <c r="B11" s="20" t="n">
-        <v>0.1678</v>
-      </c>
-      <c r="C11" s="20" t="n">
-        <v>0.1756</v>
-      </c>
-      <c r="D11" s="20" t="n">
-        <v>0.1846</v>
-      </c>
-      <c r="E11" s="20" t="n">
-        <v>0.179</v>
-      </c>
-      <c r="F11" s="20" t="n">
-        <v>0.1835</v>
+        <v>3605</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>-8672</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>-12277</v>
       </c>
     </row>
   </sheetData>
@@ -1718,45 +1588,200 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="90" customWidth="1" min="1" max="1"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="19" t="inlineStr">
-        <is>
-          <t>口径说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="21" t="inlineStr">
-        <is>
-          <t>本报告仅基于《天猫旗舰店周报》店铺合计数据，不能定位到具体商品ID。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
-        <is>
-          <t>下降主因规则：当周推广后利润环比为负时，比较“推广前利润减少”与“推广投入增加”谁贡献更大。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
-        <is>
-          <t>6.1-6.7 至 6.22-6.28 四周推广后利润同为3605，疑似异常，不作为基线。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
-        <is>
-          <t>若需ID级归因，请提供对应周的《天猫ID周损益》文件。</t>
-        </is>
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>关键周绝对数（修订后）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>指标</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>7.6-7.12</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>7.13-7.19</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>7.20-7.26</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>7.27-8.2</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>8.3-8.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>GMV</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="n">
+        <v>131865</v>
+      </c>
+      <c r="C4" s="14" t="n">
+        <v>109087</v>
+      </c>
+      <c r="D4" s="14" t="n">
+        <v>107560</v>
+      </c>
+      <c r="E4" s="14" t="n">
+        <v>118941</v>
+      </c>
+      <c r="F4" s="14" t="n">
+        <v>135684</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>去退金额</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>120260</v>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>100078</v>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>98481</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>107318</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>121296</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>推广前利润</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>16861</v>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>13701</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>13545</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>15036</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>17449</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>推广投入</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>20174</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>17570</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>18177</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>19205</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>22254</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>其他费用</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>2054</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>2405</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>2097</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>2127</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>推广后利润</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="n">
+        <v>-4109</v>
+      </c>
+      <c r="C9" s="15" t="n">
+        <v>-5144</v>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>-5582</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>-5089</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>-5821</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>推广费率</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="n">
+        <v>0.1678</v>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>0.1756</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>0.1846</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>0.1835</v>
       </c>
     </row>
   </sheetData>

--- a/新建文件夹 (2)/旗舰店周报_利润下降原因分析.xlsx
+++ b/新建文件夹 (2)/旗舰店周报_利润下降原因分析.xlsx
@@ -7,9 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="01-利润下降原因" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="02-相对上一版变化" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="03-关键周对比" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="01-近三个月结论" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="02-近三个月总览" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="03-五阶段明细" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="04-口径说明" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -69,6 +70,16 @@
       <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00C65911"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="7">
@@ -130,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -153,13 +164,16 @@
     <xf numFmtId="3" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -177,10 +191,15 @@
     <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -270,7 +289,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>推广后利润周趋势（修订后）</a:t>
+              <a:t>近三个月推广后利润</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -284,7 +303,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'01-利润下降原因'!G24</f>
+              <f>'01-近三个月结论'!H29</f>
             </strRef>
           </tx>
           <spPr>
@@ -302,12 +321,133 @@
           </marker>
           <cat>
             <numRef>
-              <f>'01-利润下降原因'!$A$25:$A$37</f>
+              <f>'01-近三个月结论'!$A$30:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'01-利润下降原因'!$G$25:$G$37</f>
+              <f>'01-近三个月结论'!$H$30:$H$42</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>推广前利润 vs 推广投入</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'01-近三个月结论'!D29</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'01-近三个月结论'!$A$30:$A$42</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'01-近三个月结论'!$D$30:$D$42</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'01-近三个月结论'!F29</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'01-近三个月结论'!$A$30:$A$42</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'01-近三个月结论'!$F$30:$F$42</f>
             </numRef>
           </val>
         </ser>
@@ -352,7 +492,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>38</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6480000" cy="2880000"/>
@@ -365,6 +505,28 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>59</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -662,10 +824,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:K59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -675,26 +837,27 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>从《天猫旗舰店周报》（已修改）看利润下降原因</t>
+          <t>天猫旗舰店近三个月利润下降原因分析</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：天猫旗舰店周报_7.27-8.2.csv（用户修订版）｜店铺级｜推广后变化 ≈ 推广前变化 − 推广投入变化</t>
+          <t>分析窗口：5.11-5.17 → 8.3-8.9（共13周）｜店铺级周报｜单位：元</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>一、利润下降原因（按修订后数据）</t>
+          <t>一、近三个月利润下降原因</t>
         </is>
       </c>
     </row>
@@ -710,733 +873,970 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="46" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="5" t="n">
         <v>1</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>修订说明：相对上一版变化：6.1-6.7（推广后利润:3605.0-&gt;-7458.0）；6.15-6.21（推广后利润:3605.0-&gt;-7953.0）；6.22-6.28（推广后利润:3605.0-&gt;-7765.0）；6.8-6.14（推广后利润:3605.0-&gt;-8672.0）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="46" customHeight="1">
+          <t>近三个月（5.11-5.17至8.3-8.9）推广后利润周均 -6426，合计 -83535；整体持续亏损。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="6" t="n">
         <v>2</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>总览：7月较好周 7.6-7.12（推广后 -4109）后走弱；7.13 -5144 → 7.20 -5582；7.27 回升至 -5089；8.3 再降至 -5821。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="46" customHeight="1">
+          <t>窗口内最好周：7.6-7.12（-4109）；最差周：6.8-6.14（-8672）；最新周：8.3-8.9（-5821），相对最好周 -1712。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>第一波（7.6→7.13）：推广后 -4109→-5144（-1035）。推广前 -3160，推广投入 -2604 → 主要是推广前利润下降。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="46" customHeight="1">
+          <t>首周→末周：推广后 -7161→-5821（+1340）；推广前 15585→17449（+1864）；推广投入 22200→22254（+54）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="6" t="n">
         <v>4</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>第二波（7.13→7.20）：推广后 -5144→-5582（-438）。推广前 -156，推广投入 +607 → 主要是推广费上升。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="46" customHeight="1">
+          <t>逐周回落归因（仅统计推广后环比为负的周）：主要是推广前利润下降：4周，环比恶化合计 -2998；主要是推广费上升：2周，环比恶化合计 -1170。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="5" t="n">
         <v>5</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>7.27当周（相对7.20）：推广后 -5582→-5089（+493）。推广前回升超过推广费增加，利润改善。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="46" customHeight="1">
+          <t>结构结论：近三个月呈现“5-6月推广前利润偏弱 → 7.6触达相对最好 → 7月中下旬先因推广前走弱、再因推广费抬升回落 → 7.27短暂修复 → 8.3再因推广费上升恶化”。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="6" t="n">
         <v>6</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>第三波（7.27→8.3）：推广后 -5089→-5821（-732）。推广前 +2413，推广投入 +3049 → 主要是推广费上升。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="46" customHeight="1">
+          <t>一句话：近三个月利润压力=推广前利润不够稳 + 推广费在回落后反弹过快；不是单一周、单一因素。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="5" t="n">
         <v>7</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>一句话：近期利润变差 = 先是推广前利润/生意走弱，后是推广费抬升过快。店铺周报无法定位商品ID。6月推广后利润已区分：[-7458.0, -8672.0, -7953.0, -7765.0]</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>二、关键下降波次拆解</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>波次</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>对比</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
+          <t>阶段A 5月中→6月上（5.11-5.17→6.8-6.14）：推广后 -1511；推广前 -1803，推广投入 -2004 → 主要是推广前利润下降。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>阶段B 6月上→7月上（6.8-6.14→7.6-7.12）：推广后 +4563；推广前 +3079，推广投入 -22 → 本期改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>阶段C 7月上→7月中下（7.6-7.12→7.20-7.26）：推广后 -1473；推广前 -3316，推广投入 -1997 → 主要是推广前利润下降。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>阶段D 7月下改善（7.20-7.26→7.27-8.2）：推广后 +493；推广前 +1491，推广投入 +1028 → 本期改善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>阶段E 8月初再降（7.27-8.2→8.3-8.9）：推广后 -732；推广前 +2413，推广投入 +3049 → 主要是推广费上升。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>二、近三个月五阶段拆解</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>阶段</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>起点</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>终点</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>起点推广后</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>终点推广后</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>推广后变化</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
         <is>
           <t>推广前变化</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>推广投入变化</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>主因判断</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>第一波</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>7.6-7.12 → 7.13-7.19</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="n">
-        <v>-1035</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>-3160</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>-2604</v>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>GMV变化</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>主因</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>阶段A 5月中→6月上</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>5.11-5.17</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>6.8-6.14</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>-7161</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>-8672</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>-1511</v>
+      </c>
+      <c r="G21" s="9" t="n">
+        <v>-1803</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>-2004</v>
+      </c>
+      <c r="I21" s="9" t="n">
+        <v>-16446</v>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
         <is>
           <t>主要是推广前利润下降</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>第二波</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>7.13-7.19 → 7.20-7.26</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="n">
-        <v>-438</v>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>-156</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>607</v>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>五月末至六月上旬走弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>阶段B 6月上→7月上</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>6.8-6.14</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>7.6-7.12</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>-8672</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>-4109</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>4563</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>3079</v>
+      </c>
+      <c r="H22" s="11" t="n">
+        <v>-22</v>
+      </c>
+      <c r="I22" s="12" t="n">
+        <v>18007</v>
+      </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>本期改善</t>
+        </is>
+      </c>
+      <c r="K22" s="10" t="inlineStr">
+        <is>
+          <t>触底后回升到近3月最好周</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>阶段C 7月上→7月中下</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>7.6-7.12</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>7.20-7.26</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>-4109</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>-5582</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>-1473</v>
+      </c>
+      <c r="G23" s="9" t="n">
+        <v>-3316</v>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>-1997</v>
+      </c>
+      <c r="I23" s="9" t="n">
+        <v>-24305</v>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>主要是推广前利润下降</t>
+        </is>
+      </c>
+      <c r="K23" s="8" t="inlineStr">
+        <is>
+          <t>最好周后连续回落</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>阶段D 7月下改善</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>7.20-7.26</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>7.27-8.2</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>-5582</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>-5089</v>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>493</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>1491</v>
+      </c>
+      <c r="H24" s="12" t="n">
+        <v>1028</v>
+      </c>
+      <c r="I24" s="12" t="n">
+        <v>11381</v>
+      </c>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>本期改善</t>
+        </is>
+      </c>
+      <c r="K24" s="10" t="inlineStr">
+        <is>
+          <t>短暂修复</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>阶段E 8月初再降</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>7.27-8.2</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>8.3-8.9</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>-5089</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>-5821</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>-732</v>
+      </c>
+      <c r="G25" s="13" t="n">
+        <v>2413</v>
+      </c>
+      <c r="H25" s="13" t="n">
+        <v>3049</v>
+      </c>
+      <c r="I25" s="13" t="n">
+        <v>16743</v>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
         <is>
           <t>主要是推广费上升</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>改善周</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>7.20-7.26 → 7.27-8.2</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="n">
-        <v>493</v>
-      </c>
-      <c r="D19" s="12" t="n">
-        <v>1491</v>
-      </c>
-      <c r="E19" s="12" t="n">
-        <v>1028</v>
-      </c>
-      <c r="F19" s="11" t="inlineStr">
-        <is>
-          <t>本期改善</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>第三波</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>7.27-8.2 → 8.3-8.9</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="n">
-        <v>-732</v>
-      </c>
-      <c r="D20" s="10" t="n">
-        <v>2413</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>3049</v>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>主要是推广费上升</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>三、近3个月周趋势与逐周主因</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="K25" s="8" t="inlineStr">
+        <is>
+          <t>推广费抬升导致再恶化</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>三、近三个月逐周明细</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>周次</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>GMV</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>去退金额</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>推广前利润</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>推广前环比</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>推广投入</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>推广费环比</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="H29" s="4" t="inlineStr">
         <is>
           <t>推广后利润</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="I29" s="4" t="inlineStr">
         <is>
           <t>推广后环比</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="J29" s="4" t="inlineStr">
         <is>
           <t>推广费率</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="K29" s="4" t="inlineStr">
         <is>
           <t>下降主因</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>5.11-5.17</t>
         </is>
       </c>
-      <c r="B25" s="14" t="n">
+      <c r="B30" s="15" t="n">
         <v>130304</v>
       </c>
-      <c r="C25" s="14" t="n">
+      <c r="C30" s="15" t="n">
+        <v>117828</v>
+      </c>
+      <c r="D30" s="15" t="n">
         <v>15585</v>
       </c>
-      <c r="D25" s="13" t="n"/>
-      <c r="E25" s="14" t="n">
+      <c r="E30" s="14" t="n"/>
+      <c r="F30" s="15" t="n">
         <v>22200</v>
       </c>
-      <c r="F25" s="13" t="n"/>
-      <c r="G25" s="15" t="n">
+      <c r="G30" s="14" t="n"/>
+      <c r="H30" s="16" t="n">
         <v>-7161</v>
       </c>
-      <c r="H25" s="13" t="n"/>
-      <c r="I25" s="16" t="n">
+      <c r="I30" s="14" t="n"/>
+      <c r="J30" s="17" t="n">
         <v>0.1884</v>
       </c>
-      <c r="J25" s="13" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="K30" s="14" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>5.18-5.24</t>
         </is>
       </c>
-      <c r="B26" s="14" t="n">
+      <c r="B31" s="15" t="n">
         <v>139241</v>
       </c>
-      <c r="C26" s="14" t="n">
+      <c r="C31" s="15" t="n">
+        <v>123811</v>
+      </c>
+      <c r="D31" s="15" t="n">
         <v>16979</v>
       </c>
-      <c r="D26" s="14" t="n">
+      <c r="E31" s="15" t="n">
         <v>1394</v>
       </c>
-      <c r="E26" s="14" t="n">
+      <c r="F31" s="15" t="n">
         <v>23198</v>
       </c>
-      <c r="F26" s="14" t="n">
+      <c r="G31" s="15" t="n">
         <v>998</v>
       </c>
-      <c r="G26" s="15" t="n">
+      <c r="H31" s="16" t="n">
         <v>-6709</v>
       </c>
-      <c r="H26" s="14" t="n">
+      <c r="I31" s="15" t="n">
         <v>452</v>
       </c>
-      <c r="I26" s="16" t="n">
+      <c r="J31" s="17" t="n">
         <v>0.1874</v>
       </c>
-      <c r="J26" s="13" t="inlineStr">
+      <c r="K31" s="14" t="inlineStr">
         <is>
           <t>改善/持平</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>5.25-5.31</t>
         </is>
       </c>
-      <c r="B27" s="10" t="n">
+      <c r="B32" s="13" t="n">
         <v>139104</v>
       </c>
-      <c r="C27" s="10" t="n">
+      <c r="C32" s="13" t="n">
+        <v>122700</v>
+      </c>
+      <c r="D32" s="13" t="n">
         <v>16534</v>
       </c>
-      <c r="D27" s="9" t="n">
+      <c r="E32" s="9" t="n">
         <v>-445</v>
       </c>
-      <c r="E27" s="10" t="n">
+      <c r="F32" s="13" t="n">
         <v>22867</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="G32" s="9" t="n">
         <v>-331</v>
       </c>
-      <c r="G27" s="9" t="n">
+      <c r="H32" s="9" t="n">
         <v>-6842</v>
       </c>
-      <c r="H27" s="9" t="n">
+      <c r="I32" s="9" t="n">
         <v>-133</v>
       </c>
-      <c r="I27" s="17" t="n">
+      <c r="J32" s="18" t="n">
         <v>0.1864</v>
       </c>
-      <c r="J27" s="8" t="inlineStr">
+      <c r="K32" s="8" t="inlineStr">
         <is>
           <t>主要是推广前利润下降</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>6.1-6.7</t>
         </is>
       </c>
-      <c r="B28" s="10" t="n">
+      <c r="B33" s="13" t="n">
         <v>123012</v>
       </c>
-      <c r="C28" s="10" t="n">
+      <c r="C33" s="13" t="n">
+        <v>110687</v>
+      </c>
+      <c r="D33" s="13" t="n">
         <v>14905</v>
       </c>
-      <c r="D28" s="9" t="n">
+      <c r="E33" s="9" t="n">
         <v>-1629</v>
       </c>
-      <c r="E28" s="10" t="n">
+      <c r="F33" s="13" t="n">
         <v>20101</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="G33" s="9" t="n">
         <v>-2766</v>
       </c>
-      <c r="G28" s="9" t="n">
+      <c r="H33" s="9" t="n">
         <v>-7458</v>
       </c>
-      <c r="H28" s="9" t="n">
+      <c r="I33" s="9" t="n">
         <v>-616</v>
       </c>
-      <c r="I28" s="17" t="n">
+      <c r="J33" s="18" t="n">
         <v>0.1816</v>
       </c>
-      <c r="J28" s="8" t="inlineStr">
+      <c r="K33" s="8" t="inlineStr">
         <is>
           <t>主要是推广前利润下降</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>6.8-6.14</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="n">
-        <v>113858</v>
-      </c>
-      <c r="C29" s="10" t="n">
-        <v>13782</v>
-      </c>
-      <c r="D29" s="9" t="n">
-        <v>-1123</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>20196</v>
-      </c>
-      <c r="F29" s="10" t="n">
-        <v>95</v>
-      </c>
-      <c r="G29" s="9" t="n">
-        <v>-8672</v>
-      </c>
-      <c r="H29" s="9" t="n">
-        <v>-1214</v>
-      </c>
-      <c r="I29" s="17" t="n">
-        <v>0.197</v>
-      </c>
-      <c r="J29" s="8" t="inlineStr">
-        <is>
-          <t>主要是推广前利润下降</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="13" t="inlineStr">
-        <is>
-          <t>6.15-6.21</t>
-        </is>
-      </c>
-      <c r="B30" s="14" t="n">
-        <v>112643</v>
-      </c>
-      <c r="C30" s="14" t="n">
-        <v>13834</v>
-      </c>
-      <c r="D30" s="14" t="n">
-        <v>52</v>
-      </c>
-      <c r="E30" s="14" t="n">
-        <v>19490</v>
-      </c>
-      <c r="F30" s="15" t="n">
-        <v>-706</v>
-      </c>
-      <c r="G30" s="15" t="n">
-        <v>-7953</v>
-      </c>
-      <c r="H30" s="14" t="n">
-        <v>719</v>
-      </c>
-      <c r="I30" s="16" t="n">
-        <v>0.1905</v>
-      </c>
-      <c r="J30" s="13" t="inlineStr">
-        <is>
-          <t>改善/持平</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="13" t="inlineStr">
-        <is>
-          <t>6.22-6.28</t>
-        </is>
-      </c>
-      <c r="B31" s="14" t="n">
-        <v>95317</v>
-      </c>
-      <c r="C31" s="14" t="n">
-        <v>11722</v>
-      </c>
-      <c r="D31" s="15" t="n">
-        <v>-2112</v>
-      </c>
-      <c r="E31" s="14" t="n">
-        <v>17051</v>
-      </c>
-      <c r="F31" s="15" t="n">
-        <v>-2439</v>
-      </c>
-      <c r="G31" s="15" t="n">
-        <v>-7765</v>
-      </c>
-      <c r="H31" s="14" t="n">
-        <v>188</v>
-      </c>
-      <c r="I31" s="16" t="n">
-        <v>0.1956</v>
-      </c>
-      <c r="J31" s="13" t="inlineStr">
-        <is>
-          <t>改善/持平</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="13" t="inlineStr">
-        <is>
-          <t>6.29-7.5</t>
-        </is>
-      </c>
-      <c r="B32" s="14" t="n">
-        <v>100176</v>
-      </c>
-      <c r="C32" s="14" t="n">
-        <v>12985</v>
-      </c>
-      <c r="D32" s="14" t="n">
-        <v>1263</v>
-      </c>
-      <c r="E32" s="14" t="n">
-        <v>17357</v>
-      </c>
-      <c r="F32" s="14" t="n">
-        <v>306</v>
-      </c>
-      <c r="G32" s="15" t="n">
-        <v>-5230</v>
-      </c>
-      <c r="H32" s="14" t="n">
-        <v>2535</v>
-      </c>
-      <c r="I32" s="16" t="n">
-        <v>0.1888</v>
-      </c>
-      <c r="J32" s="13" t="inlineStr">
-        <is>
-          <t>改善/持平</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="13" t="inlineStr">
-        <is>
-          <t>7.6-7.12</t>
-        </is>
-      </c>
-      <c r="B33" s="14" t="n">
-        <v>131865</v>
-      </c>
-      <c r="C33" s="14" t="n">
-        <v>16861</v>
-      </c>
-      <c r="D33" s="14" t="n">
-        <v>3876</v>
-      </c>
-      <c r="E33" s="14" t="n">
-        <v>20174</v>
-      </c>
-      <c r="F33" s="14" t="n">
-        <v>2817</v>
-      </c>
-      <c r="G33" s="15" t="n">
-        <v>-4109</v>
-      </c>
-      <c r="H33" s="14" t="n">
-        <v>1121</v>
-      </c>
-      <c r="I33" s="16" t="n">
-        <v>0.1678</v>
-      </c>
-      <c r="J33" s="13" t="inlineStr">
-        <is>
-          <t>改善/持平</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
+          <t>6.8-6.14</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="n">
+        <v>113858</v>
+      </c>
+      <c r="C34" s="13" t="n">
+        <v>102504</v>
+      </c>
+      <c r="D34" s="13" t="n">
+        <v>13782</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>-1123</v>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>20196</v>
+      </c>
+      <c r="G34" s="13" t="n">
+        <v>95</v>
+      </c>
+      <c r="H34" s="9" t="n">
+        <v>-8672</v>
+      </c>
+      <c r="I34" s="9" t="n">
+        <v>-1214</v>
+      </c>
+      <c r="J34" s="18" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="K34" s="8" t="inlineStr">
+        <is>
+          <t>主要是推广前利润下降</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>6.15-6.21</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="n">
+        <v>112643</v>
+      </c>
+      <c r="C35" s="15" t="n">
+        <v>102323</v>
+      </c>
+      <c r="D35" s="15" t="n">
+        <v>13834</v>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>52</v>
+      </c>
+      <c r="F35" s="15" t="n">
+        <v>19490</v>
+      </c>
+      <c r="G35" s="16" t="n">
+        <v>-706</v>
+      </c>
+      <c r="H35" s="16" t="n">
+        <v>-7953</v>
+      </c>
+      <c r="I35" s="15" t="n">
+        <v>719</v>
+      </c>
+      <c r="J35" s="17" t="n">
+        <v>0.1905</v>
+      </c>
+      <c r="K35" s="14" t="inlineStr">
+        <is>
+          <t>改善/持平</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>6.22-6.28</t>
+        </is>
+      </c>
+      <c r="B36" s="15" t="n">
+        <v>95317</v>
+      </c>
+      <c r="C36" s="15" t="n">
+        <v>87190</v>
+      </c>
+      <c r="D36" s="15" t="n">
+        <v>11722</v>
+      </c>
+      <c r="E36" s="16" t="n">
+        <v>-2112</v>
+      </c>
+      <c r="F36" s="15" t="n">
+        <v>17051</v>
+      </c>
+      <c r="G36" s="16" t="n">
+        <v>-2439</v>
+      </c>
+      <c r="H36" s="16" t="n">
+        <v>-7765</v>
+      </c>
+      <c r="I36" s="15" t="n">
+        <v>188</v>
+      </c>
+      <c r="J36" s="17" t="n">
+        <v>0.1956</v>
+      </c>
+      <c r="K36" s="14" t="inlineStr">
+        <is>
+          <t>改善/持平</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>6.29-7.5</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="n">
+        <v>100176</v>
+      </c>
+      <c r="C37" s="15" t="n">
+        <v>91929</v>
+      </c>
+      <c r="D37" s="15" t="n">
+        <v>12985</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>1263</v>
+      </c>
+      <c r="F37" s="15" t="n">
+        <v>17357</v>
+      </c>
+      <c r="G37" s="15" t="n">
+        <v>306</v>
+      </c>
+      <c r="H37" s="16" t="n">
+        <v>-5230</v>
+      </c>
+      <c r="I37" s="15" t="n">
+        <v>2535</v>
+      </c>
+      <c r="J37" s="17" t="n">
+        <v>0.1888</v>
+      </c>
+      <c r="K37" s="14" t="inlineStr">
+        <is>
+          <t>改善/持平</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>7.6-7.12</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="n">
+        <v>131865</v>
+      </c>
+      <c r="C38" s="12" t="n">
+        <v>120260</v>
+      </c>
+      <c r="D38" s="12" t="n">
+        <v>16861</v>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>3876</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>20174</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>2817</v>
+      </c>
+      <c r="H38" s="11" t="n">
+        <v>-4109</v>
+      </c>
+      <c r="I38" s="12" t="n">
+        <v>1121</v>
+      </c>
+      <c r="J38" s="19" t="n">
+        <v>0.1678</v>
+      </c>
+      <c r="K38" s="10" t="inlineStr">
+        <is>
+          <t>改善/持平</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
           <t>7.13-7.19</t>
         </is>
       </c>
-      <c r="B34" s="10" t="n">
+      <c r="B39" s="13" t="n">
         <v>109087</v>
       </c>
-      <c r="C34" s="10" t="n">
+      <c r="C39" s="13" t="n">
+        <v>100078</v>
+      </c>
+      <c r="D39" s="13" t="n">
         <v>13701</v>
       </c>
-      <c r="D34" s="9" t="n">
+      <c r="E39" s="9" t="n">
         <v>-3160</v>
       </c>
-      <c r="E34" s="10" t="n">
+      <c r="F39" s="13" t="n">
         <v>17570</v>
       </c>
-      <c r="F34" s="9" t="n">
+      <c r="G39" s="9" t="n">
         <v>-2604</v>
       </c>
-      <c r="G34" s="9" t="n">
+      <c r="H39" s="9" t="n">
         <v>-5144</v>
       </c>
-      <c r="H34" s="9" t="n">
+      <c r="I39" s="9" t="n">
         <v>-1035</v>
       </c>
-      <c r="I34" s="17" t="n">
+      <c r="J39" s="18" t="n">
         <v>0.1756</v>
       </c>
-      <c r="J34" s="8" t="inlineStr">
+      <c r="K39" s="8" t="inlineStr">
         <is>
           <t>主要是推广前利润下降</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>7.20-7.26</t>
         </is>
       </c>
-      <c r="B35" s="10" t="n">
+      <c r="B40" s="13" t="n">
         <v>107560</v>
       </c>
-      <c r="C35" s="10" t="n">
+      <c r="C40" s="13" t="n">
+        <v>98481</v>
+      </c>
+      <c r="D40" s="13" t="n">
         <v>13545</v>
       </c>
-      <c r="D35" s="9" t="n">
+      <c r="E40" s="9" t="n">
         <v>-156</v>
       </c>
-      <c r="E35" s="10" t="n">
+      <c r="F40" s="13" t="n">
         <v>18177</v>
       </c>
-      <c r="F35" s="10" t="n">
+      <c r="G40" s="13" t="n">
         <v>607</v>
       </c>
-      <c r="G35" s="9" t="n">
+      <c r="H40" s="9" t="n">
         <v>-5582</v>
       </c>
-      <c r="H35" s="9" t="n">
+      <c r="I40" s="9" t="n">
         <v>-438</v>
       </c>
-      <c r="I35" s="17" t="n">
+      <c r="J40" s="18" t="n">
         <v>0.1846</v>
       </c>
-      <c r="J35" s="8" t="inlineStr">
+      <c r="K40" s="8" t="inlineStr">
         <is>
           <t>主要是推广费上升</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="13" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
         <is>
           <t>7.27-8.2</t>
         </is>
       </c>
-      <c r="B36" s="14" t="n">
+      <c r="B41" s="15" t="n">
         <v>118941</v>
       </c>
-      <c r="C36" s="14" t="n">
+      <c r="C41" s="15" t="n">
+        <v>107318</v>
+      </c>
+      <c r="D41" s="15" t="n">
         <v>15036</v>
       </c>
-      <c r="D36" s="14" t="n">
+      <c r="E41" s="15" t="n">
         <v>1491</v>
       </c>
-      <c r="E36" s="14" t="n">
+      <c r="F41" s="15" t="n">
         <v>19205</v>
       </c>
-      <c r="F36" s="14" t="n">
+      <c r="G41" s="15" t="n">
         <v>1028</v>
       </c>
-      <c r="G36" s="15" t="n">
+      <c r="H41" s="16" t="n">
         <v>-5089</v>
       </c>
-      <c r="H36" s="14" t="n">
+      <c r="I41" s="15" t="n">
         <v>493</v>
       </c>
-      <c r="I36" s="16" t="n">
+      <c r="J41" s="17" t="n">
         <v>0.179</v>
       </c>
-      <c r="J36" s="13" t="inlineStr">
+      <c r="K41" s="14" t="inlineStr">
         <is>
           <t>改善/持平</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>8.3-8.9</t>
         </is>
       </c>
-      <c r="B37" s="10" t="n">
+      <c r="B42" s="13" t="n">
         <v>135684</v>
       </c>
-      <c r="C37" s="10" t="n">
+      <c r="C42" s="13" t="n">
+        <v>121296</v>
+      </c>
+      <c r="D42" s="13" t="n">
         <v>17449</v>
       </c>
-      <c r="D37" s="10" t="n">
+      <c r="E42" s="13" t="n">
         <v>2413</v>
       </c>
-      <c r="E37" s="10" t="n">
+      <c r="F42" s="13" t="n">
         <v>22254</v>
       </c>
-      <c r="F37" s="10" t="n">
+      <c r="G42" s="13" t="n">
         <v>3049</v>
       </c>
-      <c r="G37" s="9" t="n">
+      <c r="H42" s="9" t="n">
         <v>-5821</v>
       </c>
-      <c r="H37" s="9" t="n">
+      <c r="I42" s="9" t="n">
         <v>-732</v>
       </c>
-      <c r="I37" s="17" t="n">
+      <c r="J42" s="18" t="n">
         <v>0.1835</v>
       </c>
-      <c r="J37" s="8" t="inlineStr">
+      <c r="K42" s="8" t="inlineStr">
         <is>
           <t>主要是推广费上升</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>四、近三个月：推广前利润 vs 推广投入</t>
         </is>
       </c>
     </row>
@@ -1456,125 +1856,218 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
-        <is>
-          <t>修订版 vs 上一版差异明细</t>
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>近三个月关键指标</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>周次</t>
+          <t>指标</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>字段</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>旧值</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>新值</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>差额</t>
+          <t>数值</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>6.1-6.7</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>推广后利润</t>
-        </is>
-      </c>
-      <c r="C4" s="14" t="n">
-        <v>3605</v>
-      </c>
-      <c r="D4" s="15" t="n">
-        <v>-7458</v>
-      </c>
-      <c r="E4" s="15" t="n">
-        <v>-11063</v>
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>起始周</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>5.11-5.17</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>6.15-6.21</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>推广后利润</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="n">
-        <v>3605</v>
-      </c>
-      <c r="D5" s="15" t="n">
-        <v>-7953</v>
-      </c>
-      <c r="E5" s="15" t="n">
-        <v>-11558</v>
+      <c r="A5" s="21" t="inlineStr">
+        <is>
+          <t>结束周</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>8.3-8.9</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>6.22-6.28</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>推广后利润</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="n">
-        <v>3605</v>
-      </c>
-      <c r="D6" s="15" t="n">
-        <v>-7765</v>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>-11370</v>
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>周数</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>6.8-6.14</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>推广后利润</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="n">
-        <v>3605</v>
-      </c>
-      <c r="D7" s="15" t="n">
-        <v>-8672</v>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>-12277</v>
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>推广后利润合计</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="n">
+        <v>-83535</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>推广后利润周均</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="n">
+        <v>-6425.76923076923</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>推广前利润周均</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="n">
+        <v>14839.84615384615</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>推广投入周均</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="n">
+        <v>19987.69230769231</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>最好周</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>7.6-7.12（-4109）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>最差周</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>6.8-6.14（-8672）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>最新周相对最好周</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="n">
+        <v>-1712</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>首周→末周推广后变化</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="n">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>首周→末周推广前变化</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="n">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>首周→末周推广投入变化</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>下降周主因汇总</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>主因</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>周数</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>推广后环比合计</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>主要是推广前利润下降</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" s="16" t="n">
+        <v>-2998</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>主要是推广费上升</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" s="16" t="n">
+        <v>-1170</v>
       </c>
     </row>
   </sheetData>
@@ -1588,200 +2081,361 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
-        <is>
-          <t>关键周绝对数（修订后）</t>
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>近三个月五阶段利润变化</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>指标</t>
+          <t>阶段</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
+          <t>起点</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>终点</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>起点推广后</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>终点推广后</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>推广后变化</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>推广前变化</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>推广投入变化</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>GMV变化</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>主因</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>阶段A 5月中→6月上</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>5.11-5.17</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>6.8-6.14</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="n">
+        <v>-7161</v>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>-8672</v>
+      </c>
+      <c r="F4" s="16" t="n">
+        <v>-1511</v>
+      </c>
+      <c r="G4" s="16" t="n">
+        <v>-1803</v>
+      </c>
+      <c r="H4" s="16" t="n">
+        <v>-2004</v>
+      </c>
+      <c r="I4" s="16" t="n">
+        <v>-16446</v>
+      </c>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <t>主要是推广前利润下降</t>
+        </is>
+      </c>
+      <c r="K4" s="14" t="inlineStr">
+        <is>
+          <t>五月末至六月上旬走弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>阶段B 6月上→7月上</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>6.8-6.14</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
           <t>7.6-7.12</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>7.13-7.19</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D5" s="16" t="n">
+        <v>-8672</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>-4109</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>4563</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>3079</v>
+      </c>
+      <c r="H5" s="16" t="n">
+        <v>-22</v>
+      </c>
+      <c r="I5" s="15" t="n">
+        <v>18007</v>
+      </c>
+      <c r="J5" s="14" t="inlineStr">
+        <is>
+          <t>本期改善</t>
+        </is>
+      </c>
+      <c r="K5" s="14" t="inlineStr">
+        <is>
+          <t>触底后回升到近3月最好周</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>阶段C 7月上→7月中下</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>7.6-7.12</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>7.20-7.26</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="D6" s="16" t="n">
+        <v>-4109</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>-5582</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>-1473</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>-3316</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>-1997</v>
+      </c>
+      <c r="I6" s="16" t="n">
+        <v>-24305</v>
+      </c>
+      <c r="J6" s="14" t="inlineStr">
+        <is>
+          <t>主要是推广前利润下降</t>
+        </is>
+      </c>
+      <c r="K6" s="14" t="inlineStr">
+        <is>
+          <t>最好周后连续回落</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>阶段D 7月下改善</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>7.20-7.26</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>7.27-8.2</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="D7" s="16" t="n">
+        <v>-5582</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>-5089</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>493</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>1491</v>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>1028</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>11381</v>
+      </c>
+      <c r="J7" s="14" t="inlineStr">
+        <is>
+          <t>本期改善</t>
+        </is>
+      </c>
+      <c r="K7" s="14" t="inlineStr">
+        <is>
+          <t>短暂修复</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>阶段E 8月初再降</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>7.27-8.2</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>8.3-8.9</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>GMV</t>
-        </is>
-      </c>
-      <c r="B4" s="14" t="n">
-        <v>131865</v>
-      </c>
-      <c r="C4" s="14" t="n">
-        <v>109087</v>
-      </c>
-      <c r="D4" s="14" t="n">
-        <v>107560</v>
-      </c>
-      <c r="E4" s="14" t="n">
-        <v>118941</v>
-      </c>
-      <c r="F4" s="14" t="n">
-        <v>135684</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>去退金额</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="n">
-        <v>120260</v>
-      </c>
-      <c r="C5" s="14" t="n">
-        <v>100078</v>
-      </c>
-      <c r="D5" s="14" t="n">
-        <v>98481</v>
-      </c>
-      <c r="E5" s="14" t="n">
-        <v>107318</v>
-      </c>
-      <c r="F5" s="14" t="n">
-        <v>121296</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>推广前利润</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="n">
-        <v>16861</v>
-      </c>
-      <c r="C6" s="14" t="n">
-        <v>13701</v>
-      </c>
-      <c r="D6" s="14" t="n">
-        <v>13545</v>
-      </c>
-      <c r="E6" s="14" t="n">
-        <v>15036</v>
-      </c>
-      <c r="F6" s="14" t="n">
-        <v>17449</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>推广投入</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="n">
-        <v>20174</v>
-      </c>
-      <c r="C7" s="14" t="n">
-        <v>17570</v>
-      </c>
-      <c r="D7" s="14" t="n">
-        <v>18177</v>
-      </c>
-      <c r="E7" s="14" t="n">
-        <v>19205</v>
-      </c>
-      <c r="F7" s="14" t="n">
-        <v>22254</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>其他费用</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="n">
-        <v>2054</v>
-      </c>
-      <c r="C8" s="14" t="n">
-        <v>2405</v>
-      </c>
-      <c r="D8" s="14" t="n">
-        <v>2097</v>
-      </c>
-      <c r="E8" s="14" t="n">
-        <v>2127</v>
-      </c>
-      <c r="F8" s="14" t="n">
-        <v>2412</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>推广后利润</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="n">
-        <v>-4109</v>
-      </c>
-      <c r="C9" s="15" t="n">
-        <v>-5144</v>
-      </c>
-      <c r="D9" s="15" t="n">
-        <v>-5582</v>
-      </c>
-      <c r="E9" s="15" t="n">
+      <c r="D8" s="16" t="n">
         <v>-5089</v>
       </c>
-      <c r="F9" s="15" t="n">
+      <c r="E8" s="16" t="n">
         <v>-5821</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>推广费率</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="n">
-        <v>0.1678</v>
-      </c>
-      <c r="C10" s="19" t="n">
-        <v>0.1756</v>
-      </c>
-      <c r="D10" s="19" t="n">
-        <v>0.1846</v>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>0.179</v>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>0.1835</v>
+      <c r="F8" s="16" t="n">
+        <v>-732</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>2413</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>3049</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>16743</v>
+      </c>
+      <c r="J8" s="14" t="inlineStr">
+        <is>
+          <t>主要是推广费上升</t>
+        </is>
+      </c>
+      <c r="K8" s="14" t="inlineStr">
+        <is>
+          <t>推广费抬升导致再恶化</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="95" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>口径说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>近三个月窗口定义为 5.11-5.17 至 8.3-8.9（修订后旗舰店周报）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>利润口径：推广后利润；拆解使用推广前利润与推广投入。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>下降主因：仅在推广后环比为负的周判定；比较“推广前减少”与“推广投入增加”谁更大。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>本报告为店铺合计，不能定位商品ID；ID分析需另附周损益文件。</t>
+        </is>
       </c>
     </row>
   </sheetData>
